--- a/04_TopDown/SimsOutputs/TopDownTMDD_results.xlsx
+++ b/04_TopDown/SimsOutputs/TopDownTMDD_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Run</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">CL_L_h_kg</t>
   </si>
   <si>
+    <t xml:space="preserve">CL_RSE_pct</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vc_L_kg</t>
   </si>
   <si>
@@ -59,6 +62,15 @@
     <t xml:space="preserve">Additive_Error_nM</t>
   </si>
   <si>
+    <t xml:space="preserve">Covariance_Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hessian_Min_Eigenvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hessian_Condition_Number</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fit_Error</t>
   </si>
   <si>
@@ -77,19 +89,19 @@
     <t xml:space="preserve">Avelumab</t>
   </si>
   <si>
+    <t xml:space="preserve">Bevacizumab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golimumab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivolumab</t>
+  </si>
+  <si>
     <t xml:space="preserve">bobyqa_ierr_1</t>
   </si>
   <si>
     <t xml:space="preserve">bobyqa -- maximum number of function evaluations exceeded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bevacizumab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golimumab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nivolumab</t>
   </si>
   <si>
     <t xml:space="preserve">Pembrolizumab</t>
@@ -581,19 +593,31 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>186.787884698209</v>
+        <v>186.787823257457</v>
       </c>
       <c r="E2" t="n">
         <v>0.001</v>
@@ -608,37 +632,49 @@
         <v>0.317940972222222</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000339553653476341</v>
+        <v>0.000339700103999733</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0431995142312311</v>
+        <v>22.1790145446106</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00147431133612103</v>
+        <v>0.0432037610299405</v>
       </c>
       <c r="L2" t="n">
-        <v>0.037869453953392</v>
+        <v>0.00147684915076349</v>
       </c>
       <c r="M2" t="n">
-        <v>0.213337745195425</v>
+        <v>0.0378644373298898</v>
       </c>
       <c r="N2" t="n">
-        <v>13.1938281646862</v>
-      </c>
-      <c r="O2"/>
+        <v>0.213331540620162</v>
+      </c>
+      <c r="O2" t="n">
+        <v>13.1943906394759</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.982729038499269</v>
+      </c>
+      <c r="R2" t="n">
+        <v>185.533239801329</v>
+      </c>
+      <c r="S2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>255.836072590364</v>
+        <v>255.835977287889</v>
       </c>
       <c r="E3" t="n">
         <v>0.609</v>
@@ -653,37 +689,49 @@
         <v>621.638888888889</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000227585940291926</v>
+        <v>0.000227512896453547</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0364066002720544</v>
+        <v>7.85994236066926</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00174174068621089</v>
+        <v>0.0364051134738277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0244611345768869</v>
+        <v>0.0017417129188191</v>
       </c>
       <c r="M3" t="n">
-        <v>0.109684248662991</v>
+        <v>0.02445917752173</v>
       </c>
       <c r="N3" t="n">
-        <v>14.7332223946351</v>
-      </c>
-      <c r="O3"/>
+        <v>0.109689636777081</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14.7514790320258</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.6184512639536</v>
+      </c>
+      <c r="R3" t="n">
+        <v>294.158936686377</v>
+      </c>
+      <c r="S3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>67.3696348803654</v>
+        <v>66.8679773287333</v>
       </c>
       <c r="E4" t="n">
         <v>0.609</v>
@@ -698,39 +746,49 @@
         <v>0.158529501915709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00115633597992648</v>
+        <v>0.00115528805894328</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0431827467354741</v>
+        <v>1.83454131856161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001587406593597</v>
+        <v>0.0433627563865173</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0392283582919635</v>
+        <v>0.00155570426308289</v>
       </c>
       <c r="M4" t="n">
-        <v>0.044885876346126</v>
+        <v>0.0394483145742505</v>
       </c>
       <c r="N4" t="n">
-        <v>0.459652811704143</v>
-      </c>
-      <c r="O4" t="s">
+        <v>0.0484783644218779</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.158132486336845</v>
+      </c>
+      <c r="P4" t="s">
         <v>21</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.263309821381387</v>
+      </c>
+      <c r="R4" t="n">
+        <v>79730.9478817234</v>
+      </c>
+      <c r="S4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>316.5450407683</v>
+        <v>316.544988808862</v>
       </c>
       <c r="E5" t="n">
         <v>0.013</v>
@@ -745,37 +803,49 @@
         <v>0.307462365591398</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000320618442850687</v>
+        <v>0.000320750084352165</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0468021877251501</v>
+        <v>14.5368497604323</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00114488494981095</v>
+        <v>0.046800376552624</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0272402991433257</v>
+        <v>0.00114491891733963</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0366616570765579</v>
+        <v>0.0272466669649681</v>
       </c>
       <c r="N5" t="n">
-        <v>46.8388347167833</v>
-      </c>
-      <c r="O5"/>
+        <v>0.0366575947218518</v>
+      </c>
+      <c r="O5" t="n">
+        <v>46.8386247883205</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.05686931754676</v>
+      </c>
+      <c r="R5" t="n">
+        <v>719.748458842827</v>
+      </c>
+      <c r="S5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>84.4643294824131</v>
+        <v>84.2915918472173</v>
       </c>
       <c r="E6" t="n">
         <v>0.001</v>
@@ -790,37 +860,49 @@
         <v>0.064534121440086</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000380738068562521</v>
+        <v>0.000382190093621134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0288316207233624</v>
+        <v>5.89979940408147</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00381857064174239</v>
+        <v>0.0287825558430748</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0172595930651564</v>
+        <v>0.00388235477896165</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00332843283023909</v>
+        <v>0.0171951606714341</v>
       </c>
       <c r="N6" t="n">
-        <v>15.4031848426971</v>
-      </c>
-      <c r="O6"/>
+        <v>0.00155875807616953</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15.9430702205345</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.153308979584772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>34559.7500127193</v>
+      </c>
+      <c r="S6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>458.64317611554</v>
+        <v>458.63767953331</v>
       </c>
       <c r="E7" t="n">
         <v>0.0166</v>
@@ -835,39 +917,51 @@
         <v>1.45572368421053</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000186126922823654</v>
+        <v>0.000186143795170816</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0327443981624089</v>
+        <v>5.43095722093643</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00052208098801071</v>
+        <v>0.0327526750966299</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0138362559047838</v>
+        <v>0.000521959242950402</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2871972030013</v>
+        <v>0.0138280115725983</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00538747924113645</v>
-      </c>
-      <c r="O7" t="s">
+        <v>0.2871821358071</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000358141921558168</v>
+      </c>
+      <c r="P7" t="s">
         <v>21</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.000391822340135052</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2416434.00664627</v>
+      </c>
+      <c r="S7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>355.35189396032</v>
+        <v>355.309420946349</v>
       </c>
       <c r="E8" t="n">
         <v>0.0166</v>
@@ -882,39 +976,49 @@
         <v>0.392058823529412</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000189576697095182</v>
+        <v>0.000188921095823141</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0150120539343787</v>
+        <v>18.6208235292546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000709516485971334</v>
+        <v>0.0150184814702487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0253193431021234</v>
+        <v>0.000705507343977408</v>
       </c>
       <c r="M8" t="n">
-        <v>0.237000434657873</v>
+        <v>0.0254133495292145</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0378794114626827</v>
-      </c>
-      <c r="O8" t="s">
+        <v>0.236997874154835</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.000485712679473421</v>
+      </c>
+      <c r="P8" t="s">
         <v>21</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.000543424193542586</v>
+      </c>
+      <c r="R8" t="n">
+        <v>948603.091984457</v>
+      </c>
+      <c r="S8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>111.701856214896</v>
+        <v>111.639109037943</v>
       </c>
       <c r="E9" t="n">
         <v>2.2</v>
@@ -929,25 +1033,37 @@
         <v>1.82701973001038</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000803518347498377</v>
+        <v>0.00080027796485469</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0479086222776518</v>
+        <v>7.79056660725606</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000947442961073205</v>
+        <v>0.0480303017934882</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0204425923303938</v>
+        <v>0.000922055504152956</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0770366900235308</v>
+        <v>0.0205748310828951</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41425222657135</v>
-      </c>
-      <c r="O9" t="s">
+        <v>0.0818586120102092</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0482828434520179</v>
+      </c>
+      <c r="P9" t="s">
         <v>21</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.000850502003349596</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1737062.91262748</v>
+      </c>
+      <c r="S9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -966,81 +1082,81 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="V1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -1052,46 +1168,46 @@
         <v>79.29</v>
       </c>
       <c r="H2" t="n">
-        <v>67.9295084304398</v>
+        <v>67.9207872519142</v>
       </c>
       <c r="I2" t="n">
-        <v>0.856722265486692</v>
+        <v>0.856612274585877</v>
       </c>
       <c r="J2" t="n">
         <v>6047.62271225406</v>
       </c>
       <c r="K2" t="n">
-        <v>5893.35948948748</v>
+        <v>5892.14524866467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.974491923503429</v>
+        <v>0.97429114364652</v>
       </c>
       <c r="M2" t="n">
         <v>7396.08186805292</v>
       </c>
       <c r="N2" t="n">
-        <v>8834.33091667175</v>
+        <v>8830.51040963813</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1944609421958</v>
+        <v>1.19394438395567</v>
       </c>
       <c r="P2" t="n">
         <v>0.0340720944542953</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0285250804364184</v>
+        <v>0.0285374217695222</v>
       </c>
       <c r="R2" t="n">
-        <v>0.837197738891054</v>
+        <v>0.83755995123231</v>
       </c>
       <c r="S2" t="n">
         <v>40.7367564419863</v>
       </c>
       <c r="T2" t="n">
-        <v>38.8849547842981</v>
+        <v>38.8749797203398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.980071788320788</v>
+        <v>0.979853513461711</v>
       </c>
       <c r="V2" t="n">
         <v>10</v>
@@ -1099,16 +1215,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
         <v>0.5</v>
@@ -1120,46 +1236,46 @@
         <v>9.11</v>
       </c>
       <c r="H3" t="n">
-        <v>13.3346682267852</v>
+        <v>13.3352175461202</v>
       </c>
       <c r="I3" t="n">
-        <v>1.46373965167784</v>
+        <v>1.46379995017785</v>
       </c>
       <c r="J3" t="n">
         <v>680.455977871789</v>
       </c>
       <c r="K3" t="n">
-        <v>1008.76210605213</v>
+        <v>1008.89624724774</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48247960023389</v>
+        <v>1.48267673450852</v>
       </c>
       <c r="M3" t="n">
         <v>1086.2125929705</v>
       </c>
       <c r="N3" t="n">
-        <v>2095.032779493</v>
+        <v>2095.68156498827</v>
       </c>
       <c r="O3" t="n">
-        <v>1.92875022168878</v>
+        <v>1.92934751313934</v>
       </c>
       <c r="P3" t="n">
         <v>0.0386664638872774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0200474190242331</v>
+        <v>0.0200412127021955</v>
       </c>
       <c r="R3" t="n">
-        <v>0.518470452397106</v>
+        <v>0.518309943226791</v>
       </c>
       <c r="S3" t="n">
         <v>5.58908792824469</v>
       </c>
       <c r="T3" t="n">
-        <v>8.29630285829973</v>
+        <v>8.29683034318952</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48038222171487</v>
+        <v>1.48048778112842</v>
       </c>
       <c r="V3" t="n">
         <v>9</v>
@@ -1167,16 +1283,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -1188,46 +1304,46 @@
         <v>118.8</v>
       </c>
       <c r="H4" t="n">
-        <v>132.052743104247</v>
+        <v>132.058202137388</v>
       </c>
       <c r="I4" t="n">
-        <v>1.11155507663507</v>
+        <v>1.11160102809249</v>
       </c>
       <c r="J4" t="n">
         <v>13895.6276775864</v>
       </c>
       <c r="K4" t="n">
-        <v>15490.7848109502</v>
+        <v>15493.7418958609</v>
       </c>
       <c r="L4" t="n">
-        <v>1.11479561559762</v>
+        <v>1.11500842245883</v>
       </c>
       <c r="M4" t="n">
         <v>16019.4620961191</v>
       </c>
       <c r="N4" t="n">
-        <v>21691.2936294527</v>
+        <v>21698.2177249769</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35405880043298</v>
+        <v>1.35449103064662</v>
       </c>
       <c r="P4" t="n">
         <v>0.0262181087904162</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.019362607282662</v>
+        <v>0.019356428501339</v>
       </c>
       <c r="R4" t="n">
-        <v>0.738520365349152</v>
+        <v>0.738284696889141</v>
       </c>
       <c r="S4" t="n">
         <v>71.2276726715017</v>
       </c>
       <c r="T4" t="n">
-        <v>77.6837786452068</v>
+        <v>77.6894106751099</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0976472711035</v>
+        <v>1.09774509323022</v>
       </c>
       <c r="V4" t="n">
         <v>10</v>
@@ -1235,16 +1351,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -1256,46 +1372,46 @@
         <v>603.49</v>
       </c>
       <c r="H5" t="n">
-        <v>531.557349207364</v>
+        <v>531.579274006182</v>
       </c>
       <c r="I5" t="n">
-        <v>0.880805562987563</v>
+        <v>0.880841892999357</v>
       </c>
       <c r="J5" t="n">
         <v>69258.0459770655</v>
       </c>
       <c r="K5" t="n">
-        <v>61560.6410652678</v>
+        <v>61572.2034118392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.888859051635003</v>
+        <v>0.889025997531444</v>
       </c>
       <c r="M5" t="n">
         <v>101361.590977545</v>
       </c>
       <c r="N5" t="n">
-        <v>87746.717036961</v>
+        <v>87774.8264295384</v>
       </c>
       <c r="O5" t="n">
-        <v>0.865680147585683</v>
+        <v>0.865957465574738</v>
       </c>
       <c r="P5" t="n">
         <v>0.0165743254796797</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0191460154491289</v>
+        <v>0.0191398840457819</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15516106357403</v>
+        <v>1.15479112976559</v>
       </c>
       <c r="S5" t="n">
         <v>352.776726993411</v>
       </c>
       <c r="T5" t="n">
-        <v>315.44815558856</v>
+        <v>315.470927193198</v>
       </c>
       <c r="U5" t="n">
-        <v>0.896093448777931</v>
+        <v>0.8961720539414</v>
       </c>
       <c r="V5" t="n">
         <v>10</v>
@@ -1303,16 +1419,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -1324,46 +1440,46 @@
         <v>102.19</v>
       </c>
       <c r="H6" t="n">
-        <v>103.187745321745</v>
+        <v>102.940120823243</v>
       </c>
       <c r="I6" t="n">
-        <v>1.00976362972644</v>
+        <v>1.00734045232648</v>
       </c>
       <c r="J6" t="n">
         <v>3952.80947306448</v>
       </c>
       <c r="K6" t="n">
-        <v>3944.56949481926</v>
+        <v>3943.7158704012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.997915412239985</v>
+        <v>0.997699458391495</v>
       </c>
       <c r="M6" t="n">
         <v>4271.28080333827</v>
       </c>
       <c r="N6" t="n">
-        <v>4231.22723773687</v>
+        <v>4234.71254049836</v>
       </c>
       <c r="O6" t="n">
-        <v>0.990622586655951</v>
+        <v>0.99143857205283</v>
       </c>
       <c r="P6" t="n">
         <v>0.0983311609182295</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0992619815485596</v>
+        <v>0.0991802857887899</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0094661816421</v>
+        <v>1.00863535895062</v>
       </c>
       <c r="S6" t="n">
         <v>44.6230605704537</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6007271965976</v>
+        <v>44.5617067353474</v>
       </c>
       <c r="U6" t="n">
-        <v>1.00268915401604</v>
+        <v>1.0020304569495</v>
       </c>
       <c r="V6" t="n">
         <v>10</v>
@@ -1371,16 +1487,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -1392,46 +1508,46 @@
         <v>94.91</v>
       </c>
       <c r="H7" t="n">
-        <v>78.1570133694981</v>
+        <v>78.1588806013376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.82348554809291</v>
+        <v>0.823505221803157</v>
       </c>
       <c r="J7" t="n">
         <v>14000.6037248079</v>
       </c>
       <c r="K7" t="n">
-        <v>10720.4471656742</v>
+        <v>10716.9768808216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.765713206115418</v>
+        <v>0.765465339314757</v>
       </c>
       <c r="M7" t="n">
         <v>18042.7307100717</v>
       </c>
       <c r="N7" t="n">
-        <v>12275.4971021774</v>
+        <v>12270.4186066017</v>
       </c>
       <c r="O7" t="n">
-        <v>0.680356942606536</v>
+        <v>0.680075472154123</v>
       </c>
       <c r="P7" t="n">
         <v>0.0186224582852329</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0273716002865905</v>
+        <v>0.0273829288773593</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46981670557938</v>
+        <v>1.47042503508107</v>
       </c>
       <c r="S7" t="n">
         <v>44.1524286170874</v>
       </c>
       <c r="T7" t="n">
-        <v>38.3582463351459</v>
+        <v>38.355528166621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.844872207423681</v>
+        <v>0.844779727134424</v>
       </c>
       <c r="V7" t="n">
         <v>11</v>
@@ -1439,16 +1555,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -1460,46 +1576,46 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>105.250943887498</v>
+        <v>105.254775449607</v>
       </c>
       <c r="I8" t="n">
-        <v>1.05250943887498</v>
+        <v>1.05254775449607</v>
       </c>
       <c r="J8" t="n">
         <v>7571.8238857544</v>
       </c>
       <c r="K8" t="n">
-        <v>12556.1077853532</v>
+        <v>12552.5945146147</v>
       </c>
       <c r="L8" t="n">
-        <v>1.65826727810934</v>
+        <v>1.65780328544502</v>
       </c>
       <c r="M8" t="n">
         <v>8027.25564424347</v>
       </c>
       <c r="N8" t="n">
-        <v>15546.1958432259</v>
+        <v>15539.8328745514</v>
       </c>
       <c r="O8" t="n">
-        <v>1.93667631033708</v>
+        <v>1.93588363984587</v>
       </c>
       <c r="P8" t="n">
         <v>0.052321742151216</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0270162555673072</v>
+        <v>0.0270273176932172</v>
       </c>
       <c r="R8" t="n">
-        <v>0.516348547592834</v>
+        <v>0.51655997262295</v>
       </c>
       <c r="S8" t="n">
         <v>51.7392400057097</v>
       </c>
       <c r="T8" t="n">
-        <v>60.8986886727852</v>
+        <v>60.895786362413</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44655846276164</v>
+        <v>1.44626971166898</v>
       </c>
       <c r="V8" t="n">
         <v>11</v>
@@ -1507,16 +1623,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -1528,46 +1644,46 @@
         <v>100.73</v>
       </c>
       <c r="H9" t="n">
-        <v>100.28432304882</v>
+        <v>100.393478597271</v>
       </c>
       <c r="I9" t="n">
-        <v>0.995575529125583</v>
+        <v>0.996659174002489</v>
       </c>
       <c r="J9" t="n">
         <v>6856.4167462544</v>
       </c>
       <c r="K9" t="n">
-        <v>6764.9040839175</v>
+        <v>6752.63898714887</v>
       </c>
       <c r="L9" t="n">
-        <v>0.986652990078689</v>
+        <v>0.98486414070991</v>
       </c>
       <c r="M9" t="n">
         <v>8134.35441152585</v>
       </c>
       <c r="N9" t="n">
-        <v>7877.1377737601</v>
+        <v>7847.10695578366</v>
       </c>
       <c r="O9" t="n">
-        <v>0.968378973332992</v>
+        <v>0.964687123131102</v>
       </c>
       <c r="P9" t="n">
         <v>0.0309797172892949</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0319913155308072</v>
+        <v>0.0321137460493341</v>
       </c>
       <c r="R9" t="n">
-        <v>1.03265356594658</v>
+        <v>1.03660552320247</v>
       </c>
       <c r="S9" t="n">
         <v>55.372056701821</v>
       </c>
       <c r="T9" t="n">
-        <v>55.1494024761059</v>
+        <v>55.1426394393611</v>
       </c>
       <c r="U9" t="n">
-        <v>0.988873055290688</v>
+        <v>0.988340649744656</v>
       </c>
       <c r="V9" t="n">
         <v>10</v>
@@ -1575,16 +1691,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1596,46 +1712,46 @@
         <v>27.83</v>
       </c>
       <c r="H10" t="n">
-        <v>30.4343062599903</v>
+        <v>30.4266573646728</v>
       </c>
       <c r="I10" t="n">
-        <v>1.09357909665793</v>
+        <v>1.09330425313233</v>
       </c>
       <c r="J10" t="n">
         <v>3615.93597675492</v>
       </c>
       <c r="K10" t="n">
-        <v>4218.95115053154</v>
+        <v>4218.71848258914</v>
       </c>
       <c r="L10" t="n">
-        <v>1.16676599852793</v>
+        <v>1.16670165337805</v>
       </c>
       <c r="M10" t="n">
         <v>4124.65591218411</v>
       </c>
       <c r="N10" t="n">
-        <v>5390.06592356394</v>
+        <v>5389.55549201494</v>
       </c>
       <c r="O10" t="n">
-        <v>1.30679165446064</v>
+        <v>1.30666790315632</v>
       </c>
       <c r="P10" t="n">
         <v>0.0203653351427125</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0155842249781722</v>
+        <v>0.0155857009218019</v>
       </c>
       <c r="R10" t="n">
-        <v>0.765232924916968</v>
+        <v>0.765305398245759</v>
       </c>
       <c r="S10" t="n">
         <v>15.5860751376329</v>
       </c>
       <c r="T10" t="n">
-        <v>19.8379451686833</v>
+        <v>19.8345895212236</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26282299251473</v>
+        <v>1.26264540993346</v>
       </c>
       <c r="V10" t="n">
         <v>11</v>
@@ -1643,16 +1759,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -1664,46 +1780,46 @@
         <v>480.78</v>
       </c>
       <c r="H11" t="n">
-        <v>298.950865965327</v>
+        <v>298.877896905303</v>
       </c>
       <c r="I11" t="n">
-        <v>0.621803872801129</v>
+        <v>0.621652100555978</v>
       </c>
       <c r="J11" t="n">
         <v>58690.5719720206</v>
       </c>
       <c r="K11" t="n">
-        <v>49424.517006438</v>
+        <v>49421.0076127798</v>
       </c>
       <c r="L11" t="n">
-        <v>0.842120213617955</v>
+        <v>0.842060418772884</v>
       </c>
       <c r="M11" t="n">
         <v>62492.3230734918</v>
       </c>
       <c r="N11" t="n">
-        <v>53807.72651721</v>
+        <v>53802.669392406</v>
       </c>
       <c r="O11" t="n">
-        <v>0.86102938522435</v>
+        <v>0.860948461287531</v>
       </c>
       <c r="P11" t="n">
         <v>0.0134416510490761</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0156111408968623</v>
+        <v>0.0156126082494814</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16140054818157</v>
+        <v>1.1615097127934</v>
       </c>
       <c r="S11" t="n">
         <v>191.939665316177</v>
       </c>
       <c r="T11" t="n">
-        <v>167.664528107802</v>
+        <v>167.637654984955</v>
       </c>
       <c r="U11" t="n">
-        <v>0.917093611262352</v>
+        <v>0.916956884493775</v>
       </c>
       <c r="V11" t="n">
         <v>12</v>
@@ -1711,16 +1827,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0.3</v>
@@ -1732,46 +1848,46 @@
         <v>19.84</v>
       </c>
       <c r="H12" t="n">
-        <v>16.0402697620236</v>
+        <v>16.0516113566066</v>
       </c>
       <c r="I12" t="n">
-        <v>0.808481338811675</v>
+        <v>0.809052991764446</v>
       </c>
       <c r="J12" t="n">
         <v>866.913678413119</v>
       </c>
       <c r="K12" t="n">
-        <v>799.545400620627</v>
+        <v>799.742738173207</v>
       </c>
       <c r="L12" t="n">
-        <v>0.92228952031786</v>
+        <v>0.922517152615624</v>
       </c>
       <c r="M12" t="n">
         <v>1258.48972738551</v>
       </c>
       <c r="N12" t="n">
-        <v>1545.25228201057</v>
+        <v>1550.47868086971</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22786245162351</v>
+        <v>1.23201536502868</v>
       </c>
       <c r="P12" t="n">
         <v>0.0200240013498978</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0163080166865772</v>
+        <v>0.0162530451472345</v>
       </c>
       <c r="R12" t="n">
-        <v>0.814423471194007</v>
+        <v>0.811678188751094</v>
       </c>
       <c r="S12" t="n">
         <v>8.34270435951733</v>
       </c>
       <c r="T12" t="n">
-        <v>7.1560220240812</v>
+        <v>7.16204996161312</v>
       </c>
       <c r="U12" t="n">
-        <v>0.870177897683858</v>
+        <v>0.870728011618452</v>
       </c>
       <c r="V12" t="n">
         <v>9</v>
@@ -1779,16 +1895,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -1800,46 +1916,46 @@
         <v>79.88</v>
       </c>
       <c r="H13" t="n">
-        <v>130.028547661947</v>
+        <v>130.230509408932</v>
       </c>
       <c r="I13" t="n">
-        <v>1.62779854358972</v>
+        <v>1.6303268578985</v>
       </c>
       <c r="J13" t="n">
         <v>7202.30463503831</v>
       </c>
       <c r="K13" t="n">
-        <v>7406.8233454552</v>
+        <v>7408.32424835511</v>
       </c>
       <c r="L13" t="n">
-        <v>1.02839628713036</v>
+        <v>1.02860467916263</v>
       </c>
       <c r="M13" t="n">
         <v>18069.4524364941</v>
       </c>
       <c r="N13" t="n">
-        <v>15040.0082582794</v>
+        <v>15090.6980252993</v>
       </c>
       <c r="O13" t="n">
-        <v>0.832344439386763</v>
+        <v>0.835149713492219</v>
       </c>
       <c r="P13" t="n">
         <v>0.0139461890660863</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0167553099488011</v>
+        <v>0.0166990287379368</v>
       </c>
       <c r="R13" t="n">
-        <v>1.20142569912134</v>
+        <v>1.19739010125317</v>
       </c>
       <c r="S13" t="n">
         <v>34.0854867474344</v>
       </c>
       <c r="T13" t="n">
-        <v>49.3711834583094</v>
+        <v>49.4301670585099</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62036643054826</v>
+        <v>1.62248173779071</v>
       </c>
       <c r="V13" t="n">
         <v>9</v>
@@ -1847,16 +1963,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>30</v>
@@ -1868,46 +1984,46 @@
         <v>753.22</v>
       </c>
       <c r="H14" t="n">
-        <v>1019.9955793585</v>
+        <v>1022.1433053869</v>
       </c>
       <c r="I14" t="n">
-        <v>1.35418015899538</v>
+        <v>1.35703155172048</v>
       </c>
       <c r="J14" t="n">
         <v>62716.5872087478</v>
       </c>
       <c r="K14" t="n">
-        <v>66926.5086765508</v>
+        <v>66930.2805688579</v>
       </c>
       <c r="L14" t="n">
-        <v>1.06712612492435</v>
+        <v>1.06718626678593</v>
       </c>
       <c r="M14" t="n">
         <v>108680.911468258</v>
       </c>
       <c r="N14" t="n">
-        <v>145929.742748087</v>
+        <v>146449.959166386</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34273572770605</v>
+        <v>1.34752236789218</v>
       </c>
       <c r="P14" t="n">
         <v>0.0231871445128247</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0172685838578512</v>
+        <v>0.0172072427629491</v>
       </c>
       <c r="R14" t="n">
-        <v>0.744748187871948</v>
+        <v>0.742102709259084</v>
       </c>
       <c r="S14" t="n">
         <v>273.08326474231</v>
       </c>
       <c r="T14" t="n">
-        <v>357.858807294138</v>
+        <v>358.323820241336</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48265598067285</v>
+        <v>1.48511891724653</v>
       </c>
       <c r="V14" t="n">
         <v>9</v>
@@ -1915,16 +2031,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
@@ -1936,46 +2052,46 @@
         <v>211.015</v>
       </c>
       <c r="H15" t="n">
-        <v>201.253781057776</v>
+        <v>200.876226063373</v>
       </c>
       <c r="I15" t="n">
-        <v>0.953741587364764</v>
+        <v>0.951952354398374</v>
       </c>
       <c r="J15" t="n">
         <v>8805.20419675021</v>
       </c>
       <c r="K15" t="n">
-        <v>8926.72208123025</v>
+        <v>8933.38754309437</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01380068897492</v>
+        <v>1.01455768014914</v>
       </c>
       <c r="M15" t="n">
         <v>10808.4104919945</v>
       </c>
       <c r="N15" t="n">
-        <v>11377.2715767136</v>
+        <v>11403.2353493323</v>
       </c>
       <c r="O15" t="n">
-        <v>1.05263133604524</v>
+        <v>1.05503351836779</v>
       </c>
       <c r="P15" t="n">
         <v>0.0777172555226475</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0738314097836313</v>
+        <v>0.0736633046909083</v>
       </c>
       <c r="R15" t="n">
-        <v>0.950000219219221</v>
+        <v>0.947837184876429</v>
       </c>
       <c r="S15" t="n">
         <v>117.056284011044</v>
       </c>
       <c r="T15" t="n">
-        <v>116.1547142432</v>
+        <v>116.136581800295</v>
       </c>
       <c r="U15" t="n">
-        <v>1.00347387883396</v>
+        <v>1.00348729110187</v>
       </c>
       <c r="V15" t="n">
         <v>9</v>
@@ -1997,39 +2113,39 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
         <v>299</v>
@@ -2058,10 +2174,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
         <v>0.0467</v>
@@ -2090,10 +2206,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
         <v>1.45</v>
@@ -2122,10 +2238,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" t="n">
         <v>0.31</v>
@@ -2154,10 +2270,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
         <v>0.058</v>
@@ -2186,10 +2302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
         <v>1.34</v>
@@ -2218,10 +2334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
         <v>0.127</v>
@@ -2250,10 +2366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
         <v>0.018</v>
@@ -2296,19 +2412,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
@@ -2316,7 +2432,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -2328,18 +2444,18 @@
         <v>512.905405405405</v>
       </c>
       <c r="E2" t="n">
-        <v>458.983165070539</v>
+        <v>458.92423818861</v>
       </c>
       <c r="F2" t="n">
-        <v>67.9295084304398</v>
+        <v>67.9207872519142</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -2351,18 +2467,18 @@
         <v>357.972972972973</v>
       </c>
       <c r="E3" t="n">
-        <v>433.943261712162</v>
+        <v>433.855976369182</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2236027333999</v>
+        <v>64.210684502639</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -2374,18 +2490,18 @@
         <v>300.608108108108</v>
       </c>
       <c r="E4" t="n">
-        <v>414.282842776196</v>
+        <v>414.176431969159</v>
       </c>
       <c r="F4" t="n">
-        <v>61.3138607308769</v>
+        <v>61.2981119314355</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -2397,18 +2513,18 @@
         <v>535.743243243243</v>
       </c>
       <c r="E5" t="n">
-        <v>379.885286608268</v>
+        <v>379.752812670911</v>
       </c>
       <c r="F5" t="n">
-        <v>56.2230224180237</v>
+        <v>56.2034162752949</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -2420,18 +2536,18 @@
         <v>260.608108108108</v>
       </c>
       <c r="E6" t="n">
-        <v>342.925614374562</v>
+        <v>342.77718227747</v>
       </c>
       <c r="F6" t="n">
-        <v>50.7529909274352</v>
+        <v>50.7310229770655</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -2443,18 +2559,18 @@
         <v>403.783783783784</v>
       </c>
       <c r="E7" t="n">
-        <v>310.733926814581</v>
+        <v>310.583699479763</v>
       </c>
       <c r="F7" t="n">
-        <v>45.9886211685579</v>
+        <v>45.9663875230049</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -2466,18 +2582,18 @@
         <v>258.445945945946</v>
       </c>
       <c r="E8" t="n">
-        <v>241.314399197772</v>
+        <v>241.210866645247</v>
       </c>
       <c r="F8" t="n">
-        <v>35.7145310812703</v>
+        <v>35.6992082634966</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -2489,18 +2605,18 @@
         <v>175.27027027027</v>
       </c>
       <c r="E9" t="n">
-        <v>237.67015070091</v>
+        <v>237.571402662672</v>
       </c>
       <c r="F9" t="n">
-        <v>35.1751823037346</v>
+        <v>35.1605675940755</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -2512,18 +2628,18 @@
         <v>203.445945945946</v>
       </c>
       <c r="E10" t="n">
-        <v>191.725543257386</v>
+        <v>191.701293546462</v>
       </c>
       <c r="F10" t="n">
-        <v>28.3753804020931</v>
+        <v>28.3717914448764</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -2535,18 +2651,18 @@
         <v>140.405405405405</v>
       </c>
       <c r="E11" t="n">
-        <v>190.656764981956</v>
+        <v>190.634180609984</v>
       </c>
       <c r="F11" t="n">
-        <v>28.2172012173295</v>
+        <v>28.2138587302776</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -2558,18 +2674,18 @@
         <v>219.527027027027</v>
       </c>
       <c r="E12" t="n">
-        <v>169.801589188054</v>
+        <v>169.797620726719</v>
       </c>
       <c r="F12" t="n">
-        <v>25.130635199832</v>
+        <v>25.1300478675544</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -2581,18 +2697,18 @@
         <v>102.297297297297</v>
       </c>
       <c r="E13" t="n">
-        <v>152.693764406197</v>
+        <v>152.688595423489</v>
       </c>
       <c r="F13" t="n">
-        <v>22.5986771321172</v>
+        <v>22.5979121226763</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -2604,18 +2720,18 @@
         <v>196.959459459459</v>
       </c>
       <c r="E14" t="n">
-        <v>139.187661714341</v>
+        <v>139.177592214906</v>
       </c>
       <c r="F14" t="n">
-        <v>20.5997739337225</v>
+        <v>20.5982836478061</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -2627,18 +2743,18 @@
         <v>155</v>
       </c>
       <c r="E15" t="n">
-        <v>115.190944234885</v>
+        <v>115.171397776582</v>
       </c>
       <c r="F15" t="n">
-        <v>17.048259746763</v>
+        <v>17.0453668709341</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -2650,18 +2766,18 @@
         <v>72.2297297297297</v>
       </c>
       <c r="E16" t="n">
-        <v>114.455479609419</v>
+        <v>114.435670461499</v>
       </c>
       <c r="F16" t="n">
-        <v>16.9394109821939</v>
+        <v>16.9364792283019</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -2673,18 +2789,18 @@
         <v>109.459459459459</v>
       </c>
       <c r="E17" t="n">
-        <v>86.5181834333047</v>
+        <v>86.4905950103606</v>
       </c>
       <c r="F17" t="n">
-        <v>12.8046911481291</v>
+        <v>12.8006080615334</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -2696,18 +2812,18 @@
         <v>47.0945945945946</v>
       </c>
       <c r="E18" t="n">
-        <v>78.5705636852679</v>
+        <v>78.5415374133386</v>
       </c>
       <c r="F18" t="n">
-        <v>11.6284434254196</v>
+        <v>11.6241475371741</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B19" t="n">
         <v>2</v>
@@ -2719,18 +2835,18 @@
         <v>63.2638888888889</v>
       </c>
       <c r="E19" t="n">
-        <v>92.6018626860081</v>
+        <v>92.6056774036123</v>
       </c>
       <c r="F19" t="n">
-        <v>13.3346682267852</v>
+        <v>13.3352175461202</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
         <v>2</v>
@@ -2742,18 +2858,18 @@
         <v>42.7777777777778</v>
       </c>
       <c r="E20" t="n">
-        <v>66.501179606741</v>
+        <v>66.5048123130432</v>
       </c>
       <c r="F20" t="n">
-        <v>9.5761698633707</v>
+        <v>9.57669297307822</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
@@ -2765,18 +2881,18 @@
         <v>34.375</v>
       </c>
       <c r="E21" t="n">
-        <v>50.4037740672634</v>
+        <v>50.4084089318741</v>
       </c>
       <c r="F21" t="n">
-        <v>7.25814346568593</v>
+        <v>7.25881088618987</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
@@ -2788,18 +2904,18 @@
         <v>30.2083333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>41.1407357971058</v>
+        <v>41.1465626942419</v>
       </c>
       <c r="F22" t="n">
-        <v>5.92426595478324</v>
+        <v>5.92510502797083</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
@@ -2811,18 +2927,18 @@
         <v>21.6666666666667</v>
       </c>
       <c r="E23" t="n">
-        <v>33.8320777479461</v>
+        <v>33.8385025547184</v>
       </c>
       <c r="F23" t="n">
-        <v>4.87181919570424</v>
+        <v>4.87274436787945</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
         <v>2</v>
@@ -2834,18 +2950,18 @@
         <v>17.2222222222222</v>
       </c>
       <c r="E24" t="n">
-        <v>28.9210081343181</v>
+        <v>28.9276179324751</v>
       </c>
       <c r="F24" t="n">
-        <v>4.16462517134181</v>
+        <v>4.16557698227641</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
@@ -2857,18 +2973,18 @@
         <v>825</v>
       </c>
       <c r="E25" t="n">
-        <v>917.032938223937</v>
+        <v>917.070848176303</v>
       </c>
       <c r="F25" t="n">
-        <v>132.052743104247</v>
+        <v>132.058202137388</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>4</v>
@@ -2880,18 +2996,18 @@
         <v>654.305555555556</v>
       </c>
       <c r="E26" t="n">
-        <v>672.611746020925</v>
+        <v>672.648027634009</v>
       </c>
       <c r="F26" t="n">
-        <v>96.8560914270132</v>
+        <v>96.8613159792973</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
@@ -2903,18 +3019,18 @@
         <v>482.638888888889</v>
       </c>
       <c r="E27" t="n">
-        <v>529.715725047865</v>
+        <v>529.759673513414</v>
       </c>
       <c r="F27" t="n">
-        <v>76.2790644068925</v>
+        <v>76.2853929859317</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
@@ -2926,18 +3042,18 @@
         <v>411.736111111111</v>
       </c>
       <c r="E28" t="n">
-        <v>455.761260653701</v>
+        <v>455.815130940325</v>
       </c>
       <c r="F28" t="n">
-        <v>65.6296215341329</v>
+        <v>65.6373788554068</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
@@ -2949,18 +3065,18 @@
         <v>331.736111111111</v>
       </c>
       <c r="E29" t="n">
-        <v>374.620365637796</v>
+        <v>374.683487880212</v>
       </c>
       <c r="F29" t="n">
-        <v>53.9453326518426</v>
+        <v>53.9544222547505</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
@@ -2972,18 +3088,18 @@
         <v>271.111111111111</v>
       </c>
       <c r="E30" t="n">
-        <v>320.295623062383</v>
+        <v>320.362413720709</v>
       </c>
       <c r="F30" t="n">
-        <v>46.1225697209832</v>
+        <v>46.1321875757821</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
@@ -2995,18 +3111,18 @@
         <v>238.263888888889</v>
       </c>
       <c r="E31" t="n">
-        <v>267.069205390316</v>
+        <v>267.137309078203</v>
       </c>
       <c r="F31" t="n">
-        <v>38.4579655762055</v>
+        <v>38.4677725072612</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
@@ -3018,18 +3134,18 @@
         <v>218.75</v>
       </c>
       <c r="E32" t="n">
-        <v>222.631471789301</v>
+        <v>222.698620075445</v>
       </c>
       <c r="F32" t="n">
-        <v>32.0589319376594</v>
+        <v>32.0686012908641</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
@@ -3041,18 +3157,18 @@
         <v>189.513888888889</v>
       </c>
       <c r="E33" t="n">
-        <v>185.483845105058</v>
+        <v>185.54847236504</v>
       </c>
       <c r="F33" t="n">
-        <v>26.7096736951284</v>
+        <v>26.7189800205658</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
@@ -3064,18 +3180,18 @@
         <v>72.7777777777778</v>
       </c>
       <c r="E34" t="n">
-        <v>159.056539774189</v>
+        <v>159.118236022687</v>
       </c>
       <c r="F34" t="n">
-        <v>22.9041417274832</v>
+        <v>22.913025987267</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
@@ -3087,18 +3203,18 @@
         <v>4190.90277777778</v>
       </c>
       <c r="E35" t="n">
-        <v>3691.3704806067</v>
+        <v>3691.52273615404</v>
       </c>
       <c r="F35" t="n">
-        <v>531.557349207364</v>
+        <v>531.579274006182</v>
       </c>
       <c r="G35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
@@ -3110,18 +3226,18 @@
         <v>2833.68055555556</v>
       </c>
       <c r="E36" t="n">
-        <v>2533.67876846681</v>
+        <v>2533.82823078953</v>
       </c>
       <c r="F36" t="n">
-        <v>364.84974265922</v>
+        <v>364.871265233692</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
@@ -3133,18 +3249,18 @@
         <v>2151.73611111111</v>
       </c>
       <c r="E37" t="n">
-        <v>2077.56557680589</v>
+        <v>2077.74617494228</v>
       </c>
       <c r="F37" t="n">
-        <v>299.169443060048</v>
+        <v>299.195449191688</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
@@ -3156,18 +3272,18 @@
         <v>1918.61111111111</v>
       </c>
       <c r="E38" t="n">
-        <v>1688.06865102955</v>
+        <v>1688.30228923363</v>
       </c>
       <c r="F38" t="n">
-        <v>243.081885748255</v>
+        <v>243.115529649642</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
@@ -3179,18 +3295,18 @@
         <v>1591.11111111111</v>
       </c>
       <c r="E39" t="n">
-        <v>1418.25070524049</v>
+        <v>1418.51039121579</v>
       </c>
       <c r="F39" t="n">
-        <v>204.228101554631</v>
+        <v>204.265496335074</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B40" t="n">
         <v>3</v>
@@ -3202,18 +3318,18 @@
         <v>1338.95833333333</v>
       </c>
       <c r="E40" t="n">
-        <v>1169.74988349451</v>
+        <v>1170.02188857136</v>
       </c>
       <c r="F40" t="n">
-        <v>168.44398322321</v>
+        <v>168.483151954276</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B41" t="n">
         <v>3</v>
@@ -3225,18 +3341,18 @@
         <v>775.069444444444</v>
       </c>
       <c r="E41" t="n">
-        <v>663.94022973067</v>
+        <v>664.191440506566</v>
       </c>
       <c r="F41" t="n">
-        <v>95.6073930812165</v>
+        <v>95.6435674329456</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B42" t="n">
         <v>5</v>
@@ -3248,18 +3364,18 @@
         <v>695.170068027211</v>
       </c>
       <c r="E42" t="n">
-        <v>701.95745116833</v>
+        <v>700.27293077036</v>
       </c>
       <c r="F42" t="n">
-        <v>103.187745321745</v>
+        <v>102.940120823243</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B43" t="n">
         <v>5</v>
@@ -3271,18 +3387,18 @@
         <v>530</v>
       </c>
       <c r="E43" t="n">
-        <v>514.823373921554</v>
+        <v>515.492989268199</v>
       </c>
       <c r="F43" t="n">
-        <v>75.6790359664685</v>
+        <v>75.7774694224252</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B44" t="n">
         <v>5</v>
@@ -3294,18 +3410,18 @@
         <v>252.721088435374</v>
       </c>
       <c r="E44" t="n">
-        <v>268.15151715202</v>
+        <v>268.540988769404</v>
       </c>
       <c r="F44" t="n">
-        <v>39.418273021347</v>
+        <v>39.4755253491024</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B45" t="n">
         <v>5</v>
@@ -3317,18 +3433,18 @@
         <v>181.08843537415</v>
       </c>
       <c r="E45" t="n">
-        <v>163.468507646867</v>
+        <v>162.735384903987</v>
       </c>
       <c r="F45" t="n">
-        <v>24.0298706240894</v>
+        <v>23.922101580886</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B46" t="n">
         <v>5</v>
@@ -3340,18 +3456,18 @@
         <v>118.163265306122</v>
       </c>
       <c r="E46" t="n">
-        <v>118.07176126628</v>
+        <v>117.520999047128</v>
       </c>
       <c r="F46" t="n">
-        <v>17.3565489061432</v>
+        <v>17.2755868599278</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B47" t="n">
         <v>5</v>
@@ -3363,18 +3479,18 @@
         <v>84.6938775510204</v>
       </c>
       <c r="E47" t="n">
-        <v>91.1933702464707</v>
+        <v>90.934007582441</v>
       </c>
       <c r="F47" t="n">
-        <v>13.4054254262312</v>
+        <v>13.3672991146188</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B48" t="n">
         <v>5</v>
@@ -3386,18 +3502,18 @@
         <v>65.9863945578231</v>
       </c>
       <c r="E48" t="n">
-        <v>67.7278359513695</v>
+        <v>67.7160247621301</v>
       </c>
       <c r="F48" t="n">
-        <v>9.95599188485131</v>
+        <v>9.95425564003312</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B49" t="n">
         <v>5</v>
@@ -3409,18 +3525,18 @@
         <v>49.3197278911565</v>
       </c>
       <c r="E49" t="n">
-        <v>50.456422632374</v>
+        <v>50.5878312902047</v>
       </c>
       <c r="F49" t="n">
-        <v>7.41709412695898</v>
+        <v>7.4364111996601</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B50" t="n">
         <v>5</v>
@@ -3432,18 +3548,18 @@
         <v>38.4353741496599</v>
       </c>
       <c r="E50" t="n">
-        <v>37.7996721086842</v>
+        <v>38.0026138945335</v>
       </c>
       <c r="F50" t="n">
-        <v>5.55655179997658</v>
+        <v>5.58638424249643</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B51" t="n">
         <v>5</v>
@@ -3455,18 +3571,18 @@
         <v>26.1224489795918</v>
       </c>
       <c r="E51" t="n">
-        <v>26.6227448896506</v>
+        <v>26.8560583355281</v>
       </c>
       <c r="F51" t="n">
-        <v>3.91354349877864</v>
+        <v>3.94784057532263</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B52" t="n">
         <v>5</v>
@@ -3478,18 +3594,18 @@
         <v>17.0748299319728</v>
       </c>
       <c r="E52" t="n">
-        <v>15.8393478687567</v>
+        <v>16.0597885927275</v>
       </c>
       <c r="F52" t="n">
-        <v>2.32838413670724</v>
+        <v>2.36078892313094</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B53" t="n">
         <v>6</v>
@@ -3501,18 +3617,18 @@
         <v>632.733333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>521.046755796654</v>
+        <v>521.059204008917</v>
       </c>
       <c r="F53" t="n">
-        <v>78.1570133694981</v>
+        <v>78.1588806013376</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B54" t="n">
         <v>6</v>
@@ -3524,18 +3640,18 @@
         <v>524.266666666667</v>
       </c>
       <c r="E54" t="n">
-        <v>493.077568548653</v>
+        <v>493.084185770022</v>
       </c>
       <c r="F54" t="n">
-        <v>73.9616352822979</v>
+        <v>73.9626278655034</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B55" t="n">
         <v>6</v>
@@ -3547,18 +3663,18 @@
         <v>449.466666666667</v>
       </c>
       <c r="E55" t="n">
-        <v>414.752493504745</v>
+        <v>414.741317740209</v>
       </c>
       <c r="F55" t="n">
-        <v>62.2128740257118</v>
+        <v>62.2111976610313</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B56" t="n">
         <v>6</v>
@@ -3570,18 +3686,18 @@
         <v>405.6</v>
       </c>
       <c r="E56" t="n">
-        <v>351.868665736741</v>
+        <v>351.841396972652</v>
       </c>
       <c r="F56" t="n">
-        <v>52.7802998605111</v>
+        <v>52.7762095458978</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B57" t="n">
         <v>6</v>
@@ -3593,18 +3709,18 @@
         <v>359.8</v>
       </c>
       <c r="E57" t="n">
-        <v>307.498286786101</v>
+        <v>307.458919716412</v>
       </c>
       <c r="F57" t="n">
-        <v>46.1247430179152</v>
+        <v>46.1188379574618</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B58" t="n">
         <v>6</v>
@@ -3616,18 +3732,18 @@
         <v>324.666666666667</v>
       </c>
       <c r="E58" t="n">
-        <v>280.716057488869</v>
+        <v>280.669787189611</v>
       </c>
       <c r="F58" t="n">
-        <v>42.1074086233303</v>
+        <v>42.1004680784417</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B59" t="n">
         <v>6</v>
@@ -3639,18 +3755,18 @@
         <v>298.066666666667</v>
       </c>
       <c r="E59" t="n">
-        <v>255.307071876079</v>
+        <v>255.255564511251</v>
       </c>
       <c r="F59" t="n">
-        <v>38.2960607814118</v>
+        <v>38.2883346766877</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B60" t="n">
         <v>6</v>
@@ -3662,18 +3778,18 @@
         <v>278.333333333333</v>
       </c>
       <c r="E60" t="n">
-        <v>246.423682770378</v>
+        <v>246.370787146278</v>
       </c>
       <c r="F60" t="n">
-        <v>36.9635524155567</v>
+        <v>36.9556180719417</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B61" t="n">
         <v>6</v>
@@ -3685,18 +3801,18 @@
         <v>268.933333333333</v>
       </c>
       <c r="E61" t="n">
-        <v>233.01696192046</v>
+        <v>232.96240180291</v>
       </c>
       <c r="F61" t="n">
-        <v>34.952544288069</v>
+        <v>34.9443602704365</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B62" t="n">
         <v>6</v>
@@ -3708,18 +3824,18 @@
         <v>251.133333333333</v>
       </c>
       <c r="E62" t="n">
-        <v>220.768511796773</v>
+        <v>220.712824489318</v>
       </c>
       <c r="F62" t="n">
-        <v>33.1152767695159</v>
+        <v>33.1069236733976</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B63" t="n">
         <v>6</v>
@@ -3731,18 +3847,18 @@
         <v>234.533333333333</v>
       </c>
       <c r="E63" t="n">
-        <v>211.580400720227</v>
+        <v>211.524081868023</v>
       </c>
       <c r="F63" t="n">
-        <v>31.737060108034</v>
+        <v>31.7286122802035</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B64" t="n">
         <v>6</v>
@@ -3754,18 +3870,18 @@
         <v>226.6</v>
       </c>
       <c r="E64" t="n">
-        <v>204.97364903818</v>
+        <v>204.916972602739</v>
       </c>
       <c r="F64" t="n">
-        <v>30.746047355727</v>
+        <v>30.7375458904108</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B65" t="n">
         <v>6</v>
@@ -3777,18 +3893,18 @@
         <v>208</v>
       </c>
       <c r="E65" t="n">
-        <v>192.418655622625</v>
+        <v>192.361565484309</v>
       </c>
       <c r="F65" t="n">
-        <v>28.8627983433938</v>
+        <v>28.8542348226463</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B66" t="n">
         <v>6</v>
@@ -3800,18 +3916,18 @@
         <v>197.6</v>
       </c>
       <c r="E66" t="n">
-        <v>176.908033574379</v>
+        <v>176.850742616202</v>
       </c>
       <c r="F66" t="n">
-        <v>26.5362050361568</v>
+        <v>26.5276113924302</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B67" t="n">
         <v>6</v>
@@ -3823,18 +3939,18 @@
         <v>187.666666666667</v>
       </c>
       <c r="E67" t="n">
-        <v>166.101429720861</v>
+        <v>166.044266238875</v>
       </c>
       <c r="F67" t="n">
-        <v>24.9152144581291</v>
+        <v>24.9066399358312</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B68" t="n">
         <v>6</v>
@@ -3846,18 +3962,18 @@
         <v>181.333333333333</v>
       </c>
       <c r="E68" t="n">
-        <v>157.601475412873</v>
+        <v>157.544623167378</v>
       </c>
       <c r="F68" t="n">
-        <v>23.640221311931</v>
+        <v>23.6316934751066</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B69" t="n">
         <v>6</v>
@@ -3869,18 +3985,18 @@
         <v>178.2</v>
       </c>
       <c r="E69" t="n">
-        <v>121.181603317251</v>
+        <v>121.127702143833</v>
       </c>
       <c r="F69" t="n">
-        <v>18.1772404975876</v>
+        <v>18.169155321575</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B70" t="n">
         <v>6</v>
@@ -3892,18 +4008,18 @@
         <v>135.4</v>
       </c>
       <c r="E70" t="n">
-        <v>79.4940177710734</v>
+        <v>79.4480643995397</v>
       </c>
       <c r="F70" t="n">
-        <v>11.924102665661</v>
+        <v>11.917209659931</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B71" t="n">
         <v>6</v>
@@ -3915,18 +4031,18 @@
         <v>110.2</v>
       </c>
       <c r="E71" t="n">
-        <v>58.4887573623623</v>
+        <v>58.4491147652513</v>
       </c>
       <c r="F71" t="n">
-        <v>8.77331360435434</v>
+        <v>8.7673672147877</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B72" t="n">
         <v>6</v>
@@ -3938,18 +4054,18 @@
         <v>79.6</v>
       </c>
       <c r="E72" t="n">
-        <v>40.3076773044243</v>
+        <v>40.2754428260672</v>
       </c>
       <c r="F72" t="n">
-        <v>6.04615159566364</v>
+        <v>6.04131642391008</v>
       </c>
       <c r="G72" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B73" t="n">
         <v>7</v>
@@ -3961,18 +4077,18 @@
         <v>671.140939597315</v>
       </c>
       <c r="E73" t="n">
-        <v>706.382173741599</v>
+        <v>706.407888923539</v>
       </c>
       <c r="F73" t="n">
-        <v>105.250943887498</v>
+        <v>105.254775449607</v>
       </c>
       <c r="G73" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B74" t="n">
         <v>7</v>
@@ -3984,18 +4100,18 @@
         <v>591.073825503356</v>
       </c>
       <c r="E74" t="n">
-        <v>649.080233137207</v>
+        <v>649.094544511831</v>
       </c>
       <c r="F74" t="n">
-        <v>96.7129547374439</v>
+        <v>96.7150871322628</v>
       </c>
       <c r="G74" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B75" t="n">
         <v>7</v>
@@ -4007,18 +4123,18 @@
         <v>496.442953020134</v>
       </c>
       <c r="E75" t="n">
-        <v>564.373539724366</v>
+        <v>564.369476220204</v>
       </c>
       <c r="F75" t="n">
-        <v>84.0916574189305</v>
+        <v>84.0910519568105</v>
       </c>
       <c r="G75" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B76" t="n">
         <v>7</v>
@@ -4030,18 +4146,18 @@
         <v>339.194630872483</v>
       </c>
       <c r="E76" t="n">
-        <v>419.900973232365</v>
+        <v>419.86043625774</v>
       </c>
       <c r="F76" t="n">
-        <v>62.5652450116224</v>
+        <v>62.5592050024033</v>
       </c>
       <c r="G76" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B77" t="n">
         <v>7</v>
@@ -4053,18 +4169,18 @@
         <v>263.221476510067</v>
       </c>
       <c r="E77" t="n">
-        <v>350.030394657107</v>
+        <v>349.971393634109</v>
       </c>
       <c r="F77" t="n">
-        <v>52.154528803909</v>
+        <v>52.1457376514822</v>
       </c>
       <c r="G77" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B78" t="n">
         <v>7</v>
@@ -4076,18 +4192,18 @@
         <v>174.295302013423</v>
       </c>
       <c r="E78" t="n">
-        <v>278.120541658075</v>
+        <v>278.050534657353</v>
       </c>
       <c r="F78" t="n">
-        <v>41.4399607070532</v>
+        <v>41.4295296639455</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B79" t="n">
         <v>7</v>
@@ -4099,18 +4215,18 @@
         <v>110.134228187919</v>
       </c>
       <c r="E79" t="n">
-        <v>205.413525509955</v>
+        <v>205.341700066327</v>
       </c>
       <c r="F79" t="n">
-        <v>30.6066153009832</v>
+        <v>30.5959133098827</v>
       </c>
       <c r="G79" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B80" t="n">
         <v>7</v>
@@ -4122,18 +4238,18 @@
         <v>50.6711409395973</v>
       </c>
       <c r="E80" t="n">
-        <v>138.429737860817</v>
+        <v>138.363820758257</v>
       </c>
       <c r="F80" t="n">
-        <v>20.6260309412617</v>
+        <v>20.6162092929803</v>
       </c>
       <c r="G80" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B81" t="n">
         <v>7</v>
@@ -4145,18 +4261,18 @@
         <v>21.5436241610738</v>
       </c>
       <c r="E81" t="n">
-        <v>83.4048376085051</v>
+        <v>83.3514861462969</v>
       </c>
       <c r="F81" t="n">
-        <v>12.4273208036673</v>
+        <v>12.4193714357982</v>
       </c>
       <c r="G81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B82" t="n">
         <v>8</v>
@@ -4168,18 +4284,18 @@
         <v>671.533333333333</v>
       </c>
       <c r="E82" t="n">
-        <v>668.5621536588</v>
+        <v>669.289857315138</v>
       </c>
       <c r="F82" t="n">
-        <v>100.28432304882</v>
+        <v>100.393478597271</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B83" t="n">
         <v>8</v>
@@ -4191,18 +4307,18 @@
         <v>534.4</v>
       </c>
       <c r="E83" t="n">
-        <v>542.552508669586</v>
+        <v>541.824083783235</v>
       </c>
       <c r="F83" t="n">
-        <v>81.3828763004379</v>
+        <v>81.2736125674852</v>
       </c>
       <c r="G83" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B84" t="n">
         <v>8</v>
@@ -4214,18 +4330,18 @@
         <v>444.133333333333</v>
       </c>
       <c r="E84" t="n">
-        <v>436.443374215118</v>
+        <v>436.130671105606</v>
       </c>
       <c r="F84" t="n">
-        <v>65.4665061322676</v>
+        <v>65.4196006658409</v>
       </c>
       <c r="G84" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B85" t="n">
         <v>8</v>
@@ -4237,18 +4353,18 @@
         <v>398.4</v>
       </c>
       <c r="E85" t="n">
-        <v>385.686896189755</v>
+        <v>386.265902277719</v>
       </c>
       <c r="F85" t="n">
-        <v>57.8530344284633</v>
+        <v>57.9398853416578</v>
       </c>
       <c r="G85" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B86" t="n">
         <v>8</v>
@@ -4260,18 +4376,18 @@
         <v>361.2</v>
       </c>
       <c r="E86" t="n">
-        <v>347.099222771371</v>
+        <v>347.662565345874</v>
       </c>
       <c r="F86" t="n">
-        <v>52.0648834157056</v>
+        <v>52.149384801881</v>
       </c>
       <c r="G86" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B87" t="n">
         <v>8</v>
@@ -4283,18 +4399,18 @@
         <v>255</v>
       </c>
       <c r="E87" t="n">
-        <v>285.05792103873</v>
+        <v>285.161553615431</v>
       </c>
       <c r="F87" t="n">
-        <v>42.7586881558095</v>
+        <v>42.7742330423147</v>
       </c>
       <c r="G87" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B88" t="n">
         <v>8</v>
@@ -4306,18 +4422,18 @@
         <v>214.266666666667</v>
       </c>
       <c r="E88" t="n">
-        <v>234.656082517735</v>
+        <v>234.4442332544</v>
       </c>
       <c r="F88" t="n">
-        <v>35.1984123776603</v>
+        <v>35.1666349881601</v>
       </c>
       <c r="G88" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B89" t="n">
         <v>8</v>
@@ -4329,18 +4445,18 @@
         <v>156.333333333333</v>
       </c>
       <c r="E89" t="n">
-        <v>158.984502165887</v>
+        <v>158.438778685177</v>
       </c>
       <c r="F89" t="n">
-        <v>23.847675324883</v>
+        <v>23.7658168027765</v>
       </c>
       <c r="G89" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B90" t="n">
         <v>8</v>
@@ -4352,18 +4468,18 @@
         <v>135.666666666667</v>
       </c>
       <c r="E90" t="n">
-        <v>107.494525159876</v>
+        <v>106.852827490332</v>
       </c>
       <c r="F90" t="n">
-        <v>16.1241787739814</v>
+        <v>16.0279241235497</v>
       </c>
       <c r="G90" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B91" t="n">
         <v>8</v>
@@ -4375,18 +4491,18 @@
         <v>64.7333333333333</v>
       </c>
       <c r="E91" t="n">
-        <v>59.6895898144064</v>
+        <v>59.1064614647218</v>
       </c>
       <c r="F91" t="n">
-        <v>8.95343847216096</v>
+        <v>8.86596921970827</v>
       </c>
       <c r="G91" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B92" t="n">
         <v>9</v>
@@ -4398,18 +4514,18 @@
         <v>179.246575342466</v>
       </c>
       <c r="E92" t="n">
-        <v>208.454152465687</v>
+        <v>208.401762771732</v>
       </c>
       <c r="F92" t="n">
-        <v>30.4343062599903</v>
+        <v>30.4266573646728</v>
       </c>
       <c r="G92" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B93" t="n">
         <v>9</v>
@@ -4421,18 +4537,18 @@
         <v>190.616438356164</v>
       </c>
       <c r="E93" t="n">
-        <v>206.062332700538</v>
+        <v>206.011504598444</v>
       </c>
       <c r="F93" t="n">
-        <v>30.0851005742786</v>
+        <v>30.0776796713728</v>
       </c>
       <c r="G93" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B94" t="n">
         <v>9</v>
@@ -4444,18 +4560,18 @@
         <v>155.342465753425</v>
       </c>
       <c r="E94" t="n">
-        <v>203.563203526533</v>
+        <v>203.514005511907</v>
       </c>
       <c r="F94" t="n">
-        <v>29.7202277148738</v>
+        <v>29.7130448047385</v>
       </c>
       <c r="G94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B95" t="n">
         <v>9</v>
@@ -4467,18 +4583,18 @@
         <v>165.13698630137</v>
       </c>
       <c r="E95" t="n">
-        <v>201.299522623442</v>
+        <v>201.251799526847</v>
       </c>
       <c r="F95" t="n">
-        <v>29.3897303030225</v>
+        <v>29.3827627309197</v>
       </c>
       <c r="G95" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B96" t="n">
         <v>9</v>
@@ -4490,18 +4606,18 @@
         <v>152.191780821918</v>
       </c>
       <c r="E96" t="n">
-        <v>194.664803289084</v>
+        <v>194.621392233461</v>
       </c>
       <c r="F96" t="n">
-        <v>28.4210612802062</v>
+        <v>28.4147232660852</v>
       </c>
       <c r="G96" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B97" t="n">
         <v>9</v>
@@ -4513,18 +4629,18 @@
         <v>138.767123287671</v>
       </c>
       <c r="E97" t="n">
-        <v>192.557679761878</v>
+        <v>192.515634049744</v>
       </c>
       <c r="F97" t="n">
-        <v>28.1134212452341</v>
+        <v>28.1072825712626</v>
       </c>
       <c r="G97" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B98" t="n">
         <v>9</v>
@@ -4536,18 +4652,18 @@
         <v>131.849315068493</v>
       </c>
       <c r="E98" t="n">
-        <v>179.47347457175</v>
+        <v>179.439842482206</v>
       </c>
       <c r="F98" t="n">
-        <v>26.2031272874755</v>
+        <v>26.1982170024021</v>
       </c>
       <c r="G98" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B99" t="n">
         <v>9</v>
@@ -4559,18 +4675,18 @@
         <v>121.506849315068</v>
       </c>
       <c r="E99" t="n">
-        <v>179.442589182773</v>
+        <v>179.408976786663</v>
       </c>
       <c r="F99" t="n">
-        <v>26.1986180206849</v>
+        <v>26.1937106108528</v>
       </c>
       <c r="G99" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B100" t="n">
         <v>9</v>
@@ -4582,18 +4698,18 @@
         <v>102.123287671233</v>
       </c>
       <c r="E100" t="n">
-        <v>144.156232934047</v>
+        <v>144.14394866222</v>
       </c>
       <c r="F100" t="n">
-        <v>21.0468100083709</v>
+        <v>21.0450165046841</v>
       </c>
       <c r="G100" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B101" t="n">
         <v>9</v>
@@ -4605,18 +4721,18 @@
         <v>80.6849315068493</v>
       </c>
       <c r="E101" t="n">
-        <v>119.229151506557</v>
+        <v>119.227885375832</v>
       </c>
       <c r="F101" t="n">
-        <v>17.4074561199573</v>
+        <v>17.4072712648715</v>
       </c>
       <c r="G101" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B102" t="n">
         <v>9</v>
@@ -4628,18 +4744,18 @@
         <v>93.0821917808219</v>
       </c>
       <c r="E102" t="n">
-        <v>118.840242922224</v>
+        <v>118.8390881066</v>
       </c>
       <c r="F102" t="n">
-        <v>17.3506754666447</v>
+        <v>17.3505068635636</v>
       </c>
       <c r="G102" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B103" t="n">
         <v>9</v>
@@ -4651,18 +4767,18 @@
         <v>67.8082191780822</v>
       </c>
       <c r="E103" t="n">
-        <v>78.7698050260346</v>
+        <v>78.7691792459128</v>
       </c>
       <c r="F103" t="n">
-        <v>11.500391533801</v>
+        <v>11.5003001699033</v>
       </c>
       <c r="G103" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B104" t="n">
         <v>9</v>
@@ -4674,18 +4790,18 @@
         <v>78.2191780821918</v>
       </c>
       <c r="E104" t="n">
-        <v>78.6078268376887</v>
+        <v>78.6071841823546</v>
       </c>
       <c r="F104" t="n">
-        <v>11.4767427183026</v>
+        <v>11.4766488906238</v>
       </c>
       <c r="G104" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B105" t="n">
         <v>9</v>
@@ -4697,18 +4813,18 @@
         <v>55.8219178082192</v>
       </c>
       <c r="E105" t="n">
-        <v>59.5500845294298</v>
+        <v>59.5476648778615</v>
       </c>
       <c r="F105" t="n">
-        <v>8.69431234129674</v>
+        <v>8.69395907216778</v>
       </c>
       <c r="G105" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B106" t="n">
         <v>9</v>
@@ -4720,18 +4836,18 @@
         <v>58.7671232876712</v>
       </c>
       <c r="E106" t="n">
-        <v>59.4234954225787</v>
+        <v>59.4210659296911</v>
       </c>
       <c r="F106" t="n">
-        <v>8.6758303316965</v>
+        <v>8.6754756257349</v>
       </c>
       <c r="G106" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B107" t="n">
         <v>9</v>
@@ -4743,18 +4859,18 @@
         <v>44.5890410958904</v>
       </c>
       <c r="E107" t="n">
-        <v>40.9928610668106</v>
+        <v>40.9893781984988</v>
       </c>
       <c r="F107" t="n">
-        <v>5.98495771575435</v>
+        <v>5.98444921698082</v>
       </c>
       <c r="G107" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B108" t="n">
         <v>9</v>
@@ -4766,18 +4882,18 @@
         <v>40.2054794520548</v>
       </c>
       <c r="E108" t="n">
-        <v>40.991274477158</v>
+        <v>40.9877915552404</v>
       </c>
       <c r="F108" t="n">
-        <v>5.98472607366507</v>
+        <v>5.9842175670651</v>
       </c>
       <c r="G108" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B109" t="n">
         <v>9</v>
@@ -4789,18 +4905,18 @@
         <v>23.6301369863014</v>
       </c>
       <c r="E109" t="n">
-        <v>31.0534146490121</v>
+        <v>31.0497507208482</v>
       </c>
       <c r="F109" t="n">
-        <v>4.53379853875577</v>
+        <v>4.53326360524384</v>
       </c>
       <c r="G109" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B110" t="n">
         <v>9</v>
@@ -4812,18 +4928,18 @@
         <v>25.8904109589041</v>
       </c>
       <c r="E110" t="n">
-        <v>30.9885497179749</v>
+        <v>30.9848857320965</v>
       </c>
       <c r="F110" t="n">
-        <v>4.52432825882434</v>
+        <v>4.52379331688609</v>
       </c>
       <c r="G110" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B111" t="n">
         <v>10</v>
@@ -4835,18 +4951,18 @@
         <v>1601.50684931507</v>
       </c>
       <c r="E111" t="n">
-        <v>2047.60867099539</v>
+        <v>2047.10888291304</v>
       </c>
       <c r="F111" t="n">
-        <v>298.950865965327</v>
+        <v>298.877896905303</v>
       </c>
       <c r="G111" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B112" t="n">
         <v>10</v>
@@ -4858,18 +4974,18 @@
         <v>3293.01369863014</v>
       </c>
       <c r="E112" t="n">
-        <v>2008.87014794328</v>
+        <v>2008.3956063997</v>
       </c>
       <c r="F112" t="n">
-        <v>293.295041599718</v>
+        <v>293.225758534356</v>
       </c>
       <c r="G112" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B113" t="n">
         <v>10</v>
@@ -4881,18 +4997,18 @@
         <v>2969.52054794521</v>
       </c>
       <c r="E113" t="n">
-        <v>1997.42232604593</v>
+        <v>1996.95523576795</v>
       </c>
       <c r="F113" t="n">
-        <v>291.623659602705</v>
+        <v>291.55546442212</v>
       </c>
       <c r="G113" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B114" t="n">
         <v>10</v>
@@ -4904,18 +5020,18 @@
         <v>1416.43835616438</v>
       </c>
       <c r="E114" t="n">
-        <v>1957.01608570036</v>
+        <v>1956.57525483074</v>
       </c>
       <c r="F114" t="n">
-        <v>285.724348512253</v>
+        <v>285.659987205288</v>
       </c>
       <c r="G114" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B115" t="n">
         <v>10</v>
@@ -4927,18 +5043,18 @@
         <v>2714.45205479452</v>
       </c>
       <c r="E115" t="n">
-        <v>1902.90662487856</v>
+        <v>1902.5008390777</v>
       </c>
       <c r="F115" t="n">
-        <v>277.82436723227</v>
+        <v>277.765122505343</v>
       </c>
       <c r="G115" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B116" t="n">
         <v>10</v>
@@ -4950,18 +5066,18 @@
         <v>1318.56164383562</v>
       </c>
       <c r="E116" t="n">
-        <v>1803.13677073737</v>
+        <v>1802.79510259031</v>
       </c>
       <c r="F116" t="n">
-        <v>263.257968527657</v>
+        <v>263.208084978186</v>
       </c>
       <c r="G116" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B117" t="n">
         <v>10</v>
@@ -4973,18 +5089,18 @@
         <v>2663.97260273973</v>
       </c>
       <c r="E117" t="n">
-        <v>1776.46619519764</v>
+        <v>1776.14152121432</v>
       </c>
       <c r="F117" t="n">
-        <v>259.364064498855</v>
+        <v>259.316662097291</v>
       </c>
       <c r="G117" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B118" t="n">
         <v>10</v>
@@ -4996,18 +5112,18 @@
         <v>1052.7397260274</v>
       </c>
       <c r="E118" t="n">
-        <v>1445.93515756835</v>
+        <v>1445.80995955808</v>
       </c>
       <c r="F118" t="n">
-        <v>211.106533004979</v>
+        <v>211.08825409548</v>
       </c>
       <c r="G118" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B119" t="n">
         <v>10</v>
@@ -5019,18 +5135,18 @@
         <v>2138.6301369863</v>
       </c>
       <c r="E119" t="n">
-        <v>1438.06380230253</v>
+        <v>1437.94291248784</v>
       </c>
       <c r="F119" t="n">
-        <v>209.95731513617</v>
+        <v>209.939665223224</v>
       </c>
       <c r="G119" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B120" t="n">
         <v>10</v>
@@ -5042,18 +5158,18 @@
         <v>866.712328767123</v>
       </c>
       <c r="E120" t="n">
-        <v>1194.40092005475</v>
+        <v>1194.38770514244</v>
       </c>
       <c r="F120" t="n">
-        <v>174.382534327993</v>
+        <v>174.380604950796</v>
       </c>
       <c r="G120" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B121" t="n">
         <v>10</v>
@@ -5065,18 +5181,18 @@
         <v>1767.94520547945</v>
       </c>
       <c r="E121" t="n">
-        <v>1187.69085916774</v>
+        <v>1187.67957271633</v>
       </c>
       <c r="F121" t="n">
-        <v>173.40286543849</v>
+        <v>173.401217616584</v>
       </c>
       <c r="G121" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
@@ -5088,18 +5204,18 @@
         <v>720.890410958904</v>
       </c>
       <c r="E122" t="n">
-        <v>788.77503010582</v>
+        <v>788.768939168944</v>
       </c>
       <c r="F122" t="n">
-        <v>115.16115439545</v>
+        <v>115.160265118666</v>
       </c>
       <c r="G122" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B123" t="n">
         <v>10</v>
@@ -5111,18 +5227,18 @@
         <v>983.082191780822</v>
       </c>
       <c r="E123" t="n">
-        <v>787.184614448751</v>
+        <v>787.178357849913</v>
       </c>
       <c r="F123" t="n">
-        <v>114.928953709518</v>
+        <v>114.928040246087</v>
       </c>
       <c r="G123" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B124" t="n">
         <v>10</v>
@@ -5134,18 +5250,18 @@
         <v>581.506849315069</v>
       </c>
       <c r="E124" t="n">
-        <v>596.445949732155</v>
+        <v>596.42189759189</v>
       </c>
       <c r="F124" t="n">
-        <v>87.0811086608946</v>
+        <v>87.0775970484159</v>
       </c>
       <c r="G124" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B125" t="n">
         <v>10</v>
@@ -5157,18 +5273,18 @@
         <v>858.561643835616</v>
       </c>
       <c r="E125" t="n">
-        <v>595.317268932419</v>
+        <v>595.293128936864</v>
       </c>
       <c r="F125" t="n">
-        <v>86.9163212641332</v>
+        <v>86.9127968247822</v>
       </c>
       <c r="G125" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B126" t="n">
         <v>10</v>
@@ -5180,18 +5296,18 @@
         <v>552.465753424658</v>
       </c>
       <c r="E126" t="n">
-        <v>410.780644443652</v>
+        <v>410.745938610123</v>
       </c>
       <c r="F126" t="n">
-        <v>59.9739740887731</v>
+        <v>59.968907037078</v>
       </c>
       <c r="G126" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B127" t="n">
         <v>10</v>
@@ -5203,18 +5319,18 @@
         <v>427.739726027397</v>
       </c>
       <c r="E127" t="n">
-        <v>311.35791909925</v>
+        <v>311.321391220158</v>
       </c>
       <c r="F127" t="n">
-        <v>45.4582561884905</v>
+        <v>45.4529231181431</v>
       </c>
       <c r="G127" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B128" t="n">
         <v>10</v>
@@ -5226,18 +5342,18 @@
         <v>238.698630136986</v>
       </c>
       <c r="E128" t="n">
-        <v>214.843500027053</v>
+        <v>214.808849084137</v>
       </c>
       <c r="F128" t="n">
-        <v>31.3671510039498</v>
+        <v>31.3620919662839</v>
       </c>
       <c r="G128" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B129" t="n">
         <v>10</v>
@@ -5249,18 +5365,18 @@
         <v>146.027397260274</v>
       </c>
       <c r="E129" t="n">
-        <v>162.472519448483</v>
+        <v>162.440934178613</v>
       </c>
       <c r="F129" t="n">
-        <v>23.7209878394786</v>
+        <v>23.7163763900774</v>
       </c>
       <c r="G129" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B130" t="n">
         <v>10</v>
@@ -5272,18 +5388,18 @@
         <v>120.27397260274</v>
       </c>
       <c r="E130" t="n">
-        <v>112.117728431996</v>
+        <v>112.090999682982</v>
       </c>
       <c r="F130" t="n">
-        <v>16.3691883510714</v>
+        <v>16.3652859537153</v>
       </c>
       <c r="G130" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B131" t="n">
         <v>11</v>
@@ -5295,18 +5411,18 @@
         <v>135.890410958904</v>
       </c>
       <c r="E131" t="n">
-        <v>109.864861383723</v>
+        <v>109.942543538401</v>
       </c>
       <c r="F131" t="n">
-        <v>16.0402697620236</v>
+        <v>16.0516113566066</v>
       </c>
       <c r="G131" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B132" t="n">
         <v>11</v>
@@ -5318,18 +5434,18 @@
         <v>68.4931506849315</v>
       </c>
       <c r="E132" t="n">
-        <v>64.3654731067483</v>
+        <v>64.5040679446372</v>
       </c>
       <c r="F132" t="n">
-        <v>9.39735907358525</v>
+        <v>9.41759391991703</v>
       </c>
       <c r="G132" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B133" t="n">
         <v>11</v>
@@ -5341,18 +5457,18 @@
         <v>90.0684931506849</v>
       </c>
       <c r="E133" t="n">
-        <v>56.6047950368356</v>
+        <v>56.7208176724251</v>
       </c>
       <c r="F133" t="n">
-        <v>8.264300075378</v>
+        <v>8.28123938017407</v>
       </c>
       <c r="G133" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B134" t="n">
         <v>11</v>
@@ -5364,18 +5480,18 @@
         <v>52.0547945205479</v>
       </c>
       <c r="E134" t="n">
-        <v>50.5076566315457</v>
+        <v>50.5956803570911</v>
       </c>
       <c r="F134" t="n">
-        <v>7.37411786820567</v>
+        <v>7.3869693321353</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B135" t="n">
         <v>11</v>
@@ -5387,18 +5503,18 @@
         <v>44.1780821917808</v>
       </c>
       <c r="E135" t="n">
-        <v>38.3734108563849</v>
+        <v>38.3751907690273</v>
       </c>
       <c r="F135" t="n">
-        <v>5.60251798503219</v>
+        <v>5.60277785227799</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B136" t="n">
         <v>11</v>
@@ -5410,18 +5526,18 @@
         <v>36.4383561643836</v>
       </c>
       <c r="E136" t="n">
-        <v>35.5413615636874</v>
+        <v>35.5209864035708</v>
       </c>
       <c r="F136" t="n">
-        <v>5.18903878829837</v>
+        <v>5.18606401492133</v>
       </c>
       <c r="G136" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B137" t="n">
         <v>11</v>
@@ -5433,18 +5549,18 @@
         <v>30.958904109589</v>
       </c>
       <c r="E137" t="n">
-        <v>32.0014867234648</v>
+        <v>31.9649456203805</v>
       </c>
       <c r="F137" t="n">
-        <v>4.67221706162586</v>
+        <v>4.66688206057555</v>
       </c>
       <c r="G137" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B138" t="n">
         <v>11</v>
@@ -5456,18 +5572,18 @@
         <v>37.4657534246575</v>
       </c>
       <c r="E138" t="n">
-        <v>30.7131516715919</v>
+        <v>30.6769041788043</v>
       </c>
       <c r="F138" t="n">
-        <v>4.48412014405242</v>
+        <v>4.47882801010543</v>
       </c>
       <c r="G138" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B139" t="n">
         <v>11</v>
@@ -5479,18 +5595,18 @@
         <v>23.4931506849315</v>
       </c>
       <c r="E139" t="n">
-        <v>28.0946457843927</v>
+        <v>28.0685233414611</v>
       </c>
       <c r="F139" t="n">
-        <v>4.10181828452133</v>
+        <v>4.09800440785333</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B140" t="n">
         <v>11</v>
@@ -5502,18 +5618,18 @@
         <v>30.0684931506849</v>
       </c>
       <c r="E140" t="n">
-        <v>27.5994992523282</v>
+        <v>27.5761938873576</v>
       </c>
       <c r="F140" t="n">
-        <v>4.02952689083992</v>
+        <v>4.02612430755421</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B141" t="n">
         <v>11</v>
@@ -5525,18 +5641,18 @@
         <v>21.0958904109589</v>
       </c>
       <c r="E141" t="n">
-        <v>21.1656960091457</v>
+        <v>21.1819713379767</v>
       </c>
       <c r="F141" t="n">
-        <v>3.09019161733528</v>
+        <v>3.0925678153446</v>
       </c>
       <c r="G141" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B142" t="n">
         <v>11</v>
@@ -5548,18 +5664,18 @@
         <v>16.9178082191781</v>
       </c>
       <c r="E142" t="n">
-        <v>20.824427626613</v>
+        <v>20.8426028375839</v>
       </c>
       <c r="F142" t="n">
-        <v>3.0403664334855</v>
+        <v>3.04302001428724</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B143" t="n">
         <v>12</v>
@@ -5571,18 +5687,18 @@
         <v>449.520547945205</v>
       </c>
       <c r="E143" t="n">
-        <v>890.606490835254</v>
+        <v>891.989790472139</v>
       </c>
       <c r="F143" t="n">
-        <v>130.028547661947</v>
+        <v>130.230509408932</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B144" t="n">
         <v>12</v>
@@ -5594,18 +5710,18 @@
         <v>390.616438356164</v>
       </c>
       <c r="E144" t="n">
-        <v>553.842455656929</v>
+        <v>554.954831376962</v>
       </c>
       <c r="F144" t="n">
-        <v>80.8609985259117</v>
+        <v>81.0234053810364</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B145" t="n">
         <v>12</v>
@@ -5617,18 +5733,18 @@
         <v>547.123287671233</v>
       </c>
       <c r="E145" t="n">
-        <v>455.457399986218</v>
+        <v>456.032940346637</v>
       </c>
       <c r="F145" t="n">
-        <v>66.4967803979878</v>
+        <v>66.5808092906091</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B146" t="n">
         <v>12</v>
@@ -5640,18 +5756,18 @@
         <v>339.452054794521</v>
       </c>
       <c r="E146" t="n">
-        <v>379.492863879196</v>
+        <v>379.476195843879</v>
       </c>
       <c r="F146" t="n">
-        <v>55.4059581263627</v>
+        <v>55.4035245932064</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B147" t="n">
         <v>12</v>
@@ -5663,18 +5779,18 @@
         <v>401.712328767123</v>
       </c>
       <c r="E147" t="n">
-        <v>363.883555412217</v>
+        <v>363.742494804081</v>
       </c>
       <c r="F147" t="n">
-        <v>53.1269990901838</v>
+        <v>53.1064042413958</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B148" t="n">
         <v>12</v>
@@ -5686,18 +5802,18 @@
         <v>359.041095890411</v>
       </c>
       <c r="E148" t="n">
-        <v>323.914760251399</v>
+        <v>323.555943329457</v>
       </c>
       <c r="F148" t="n">
-        <v>47.2915549967043</v>
+        <v>47.2391677261007</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B149" t="n">
         <v>12</v>
@@ -5709,18 +5825,18 @@
         <v>330.068493150685</v>
       </c>
       <c r="E149" t="n">
-        <v>287.882922753647</v>
+        <v>287.585798113554</v>
       </c>
       <c r="F149" t="n">
-        <v>42.0309067220325</v>
+        <v>41.9875265245789</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B150" t="n">
         <v>12</v>
@@ -5732,18 +5848,18 @@
         <v>193.561643835616</v>
       </c>
       <c r="E150" t="n">
-        <v>211.487429339096</v>
+        <v>211.651529401343</v>
       </c>
       <c r="F150" t="n">
-        <v>30.877164683508</v>
+        <v>30.9011232925961</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B151" t="n">
         <v>12</v>
@@ -5755,18 +5871,18 @@
         <v>303.356164383562</v>
       </c>
       <c r="E151" t="n">
-        <v>208.08018462723</v>
+        <v>208.263252827753</v>
       </c>
       <c r="F151" t="n">
-        <v>30.3797069555755</v>
+        <v>30.406434912852</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B152" t="n">
         <v>13</v>
@@ -5778,18 +5894,18 @@
         <v>4073.83561643836</v>
       </c>
       <c r="E152" t="n">
-        <v>6986.27109149658</v>
+        <v>7000.98154374589</v>
       </c>
       <c r="F152" t="n">
-        <v>1019.9955793585</v>
+        <v>1022.1433053869</v>
       </c>
       <c r="G152" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B153" t="n">
         <v>13</v>
@@ -5801,18 +5917,18 @@
         <v>5159.04109589041</v>
       </c>
       <c r="E153" t="n">
-        <v>5538.38687310167</v>
+        <v>5549.51092777353</v>
       </c>
       <c r="F153" t="n">
-        <v>808.604483472844</v>
+        <v>810.228595454935</v>
       </c>
       <c r="G153" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B154" t="n">
         <v>13</v>
@@ -5824,18 +5940,18 @@
         <v>3620.13698630137</v>
       </c>
       <c r="E154" t="n">
-        <v>4132.2155178391</v>
+        <v>4134.81406180478</v>
       </c>
       <c r="F154" t="n">
-        <v>603.303465604508</v>
+        <v>603.682853023498</v>
       </c>
       <c r="G154" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B155" t="n">
         <v>13</v>
@@ -5847,18 +5963,18 @@
         <v>2102.94520547945</v>
       </c>
       <c r="E155" t="n">
-        <v>3940.80744073371</v>
+        <v>3941.84503412484</v>
       </c>
       <c r="F155" t="n">
-        <v>575.357886347121</v>
+        <v>575.509374982227</v>
       </c>
       <c r="G155" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B156" t="n">
         <v>13</v>
@@ -5870,18 +5986,18 @@
         <v>4270.8904109589</v>
       </c>
       <c r="E156" t="n">
-        <v>3372.03022150356</v>
+        <v>3368.90208587083</v>
       </c>
       <c r="F156" t="n">
-        <v>492.31641233952</v>
+        <v>491.859704537141</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B157" t="n">
         <v>13</v>
@@ -5893,18 +6009,18 @@
         <v>2791.91780821918</v>
       </c>
       <c r="E157" t="n">
-        <v>3115.79634376</v>
+        <v>3112.12063971515</v>
       </c>
       <c r="F157" t="n">
-        <v>454.906266188961</v>
+        <v>454.369613398412</v>
       </c>
       <c r="G157" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B158" t="n">
         <v>13</v>
@@ -5916,18 +6032,18 @@
         <v>2311.30136986301</v>
       </c>
       <c r="E158" t="n">
-        <v>2794.82882153484</v>
+        <v>2792.29937494061</v>
       </c>
       <c r="F158" t="n">
-        <v>408.045007944086</v>
+        <v>407.675708741329</v>
       </c>
       <c r="G158" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B159" t="n">
         <v>13</v>
@@ -5939,18 +6055,18 @@
         <v>3068.49315068493</v>
       </c>
       <c r="E159" t="n">
-        <v>2754.30410305293</v>
+        <v>2752.00824130959</v>
       </c>
       <c r="F159" t="n">
-        <v>402.128399045728</v>
+        <v>401.7932032312</v>
       </c>
       <c r="G159" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B160" t="n">
         <v>13</v>
@@ -5962,18 +6078,18 @@
         <v>2153.21917808219</v>
       </c>
       <c r="E160" t="n">
-        <v>2130.00118614737</v>
+        <v>2131.55730468534</v>
       </c>
       <c r="F160" t="n">
-        <v>310.980173177517</v>
+        <v>311.207366484059</v>
       </c>
       <c r="G160" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B161" t="n">
         <v>13</v>
@@ -5985,18 +6101,18 @@
         <v>1913.35616438356</v>
       </c>
       <c r="E161" t="n">
-        <v>2099.94586684749</v>
+        <v>2101.67080000313</v>
       </c>
       <c r="F161" t="n">
-        <v>306.592096559734</v>
+        <v>306.843936800458</v>
       </c>
       <c r="G161" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B162" t="n">
         <v>14</v>
@@ -6008,18 +6124,18 @@
         <v>1290.57432432432</v>
       </c>
       <c r="E162" t="n">
-        <v>1359.82284498497</v>
+        <v>1357.27179772549</v>
       </c>
       <c r="F162" t="n">
-        <v>201.253781057776</v>
+        <v>200.876226063373</v>
       </c>
       <c r="G162" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B163" t="n">
         <v>14</v>
@@ -6031,18 +6147,18 @@
         <v>1425.77702702703</v>
       </c>
       <c r="E163" t="n">
-        <v>1312.28204679785</v>
+        <v>1310.6118585433</v>
       </c>
       <c r="F163" t="n">
-        <v>194.217742926082</v>
+        <v>193.970555064408</v>
       </c>
       <c r="G163" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B164" t="n">
         <v>14</v>
@@ -6054,18 +6170,18 @@
         <v>1190.97972972973</v>
       </c>
       <c r="E164" t="n">
-        <v>1267.5186485096</v>
+        <v>1266.60331194732</v>
       </c>
       <c r="F164" t="n">
-        <v>187.592759979421</v>
+        <v>187.457290168204</v>
       </c>
       <c r="G164" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B165" t="n">
         <v>14</v>
@@ -6077,18 +6193,18 @@
         <v>1158.44594594595</v>
       </c>
       <c r="E165" t="n">
-        <v>1225.34508930498</v>
+        <v>1225.07222467102</v>
       </c>
       <c r="F165" t="n">
-        <v>181.351073217138</v>
+        <v>181.310689251311</v>
       </c>
       <c r="G165" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B166" t="n">
         <v>14</v>
@@ -6100,18 +6216,18 @@
         <v>1286.72297297297</v>
       </c>
       <c r="E166" t="n">
-        <v>1148.0812864632</v>
+        <v>1148.8044070438</v>
       </c>
       <c r="F166" t="n">
-        <v>169.916030396554</v>
+        <v>170.023052242483</v>
       </c>
       <c r="G166" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B167" t="n">
         <v>14</v>
@@ -6123,18 +6239,18 @@
         <v>1079.52702702703</v>
       </c>
       <c r="E167" t="n">
-        <v>1079.23427549431</v>
+        <v>1080.63735192763</v>
       </c>
       <c r="F167" t="n">
-        <v>159.726672773158</v>
+        <v>159.934328085289</v>
       </c>
       <c r="G167" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B168" t="n">
         <v>14</v>
@@ -6146,18 +6262,18 @@
         <v>660.844594594595</v>
       </c>
       <c r="E168" t="n">
-        <v>726.935675078684</v>
+        <v>728.511875078252</v>
       </c>
       <c r="F168" t="n">
-        <v>107.586479911645</v>
+        <v>107.819757511581</v>
       </c>
       <c r="G168" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B169" t="n">
         <v>14</v>
@@ -6169,18 +6285,18 @@
         <v>552.5</v>
       </c>
       <c r="E169" t="n">
-        <v>490.671443497263</v>
+        <v>490.432839374464</v>
       </c>
       <c r="F169" t="n">
-        <v>72.619373637595</v>
+        <v>72.5840602274207</v>
       </c>
       <c r="G169" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B170" t="n">
         <v>14</v>
@@ -6192,18 +6308,18 @@
         <v>322.263513513513</v>
       </c>
       <c r="E170" t="n">
-        <v>359.88420816424</v>
+        <v>359.609453346022</v>
       </c>
       <c r="F170" t="n">
-        <v>53.2628628083075</v>
+        <v>53.2221990952113</v>
       </c>
       <c r="G170" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B171" t="n">
         <v>14</v>
@@ -6215,13 +6331,13 @@
         <v>204.662162162162</v>
       </c>
       <c r="E171" t="n">
-        <v>198.810129297854</v>
+        <v>199.502027410905</v>
       </c>
       <c r="F171" t="n">
-        <v>29.4238991360824</v>
+        <v>29.526300056814</v>
       </c>
       <c r="G171" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
